--- a/output/full_scan/batch_seq7_2026-07-02.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-02.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6505</v>
+        <v>6834</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>847.2457997024196</v>
+        <v>953.43291918395</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>57.6</v>
+        <v>130</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.40285509008999</v>
+        <v>72.00706059642425</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.00055055958519</v>
+        <v>50.02322485508736</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.302255456382722</v>
+        <v>0.1810523197622588</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3059250565951946</v>
+        <v>1.805142418797301</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6719</v>
+        <v>6505</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>833.8106205502763</v>
+        <v>847.2457997024196</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>300</v>
+        <v>57.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>65.77021992136972</v>
+        <v>60.40285509008999</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>38.68959983332374</v>
+        <v>14.00055055958519</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.681062055027633</v>
+        <v>2.302255456382722</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.641056237143719</v>
+        <v>0.3059250565951946</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6803</v>
+        <v>6719</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>833.1942979634533</v>
+        <v>833.8106205502763</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.93646325146625</v>
+        <v>65.77021992136972</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.02790895014136</v>
+        <v>38.68959983332374</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.469749273081693</v>
+        <v>3.681062055027633</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3841977735820612</v>
+        <v>2.641056237143719</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6651</v>
+        <v>6803</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>831.8165257951573</v>
+        <v>833.1942979634533</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>159</v>
+        <v>291</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.71876815813131</v>
+        <v>60.93646325146625</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30.08222519568648</v>
+        <v>28.02790895014136</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.268305475917528</v>
+        <v>2.469749273081693</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0019420571058761</v>
+        <v>0.3841977735820612</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6691</v>
+        <v>6651</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>731.3895585221532</v>
+        <v>831.8165257951573</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>766</v>
+        <v>159</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.05752987111546</v>
+        <v>59.71876815813131</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32.00199913222708</v>
+        <v>30.08222519568648</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.7713967340346711</v>
+        <v>1.268305475917528</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.703125818082032</v>
+        <v>0.0019420571058761</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6526</v>
+        <v>6691</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>697.3275598403287</v>
+        <v>731.3895585221532</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.62667437653457</v>
+        <v>61.05752987111546</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14.39109594321779</v>
+        <v>32.00199913222708</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8705496621237855</v>
+        <v>0.7713967340346711</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.384034886230331</v>
+        <v>3.703125818082032</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6560</v>
+        <v>6526</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>686.382755605983</v>
+        <v>697.3275598403287</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>40.25</v>
+        <v>705</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.58131382414293</v>
+        <v>56.62667437653457</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26.34091004635924</v>
+        <v>14.39109594321779</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.265208649129701</v>
+        <v>0.8705496621237855</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1699272135894094</v>
+        <v>1.384034886230331</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6672</v>
+        <v>6560</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>675.9953360995936</v>
+        <v>686.382755605983</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>297.5</v>
+        <v>40.25</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>69.86142548804412</v>
+        <v>59.58131382414293</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>40.02916462400808</v>
+        <v>26.34091004635924</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7855161670200822</v>
+        <v>2.265208649129701</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4.63315230199138</v>
+        <v>0.1699272135894094</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6548</v>
+        <v>6672</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>658.9680966894821</v>
+        <v>675.9953360995936</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>297.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.45098217602965</v>
+        <v>69.86142548804412</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>39.3282293003697</v>
+        <v>40.02916462400808</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.078183542491438</v>
+        <v>0.7855161670200822</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-1.605318531100165</v>
+        <v>4.63315230199138</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6491</v>
+        <v>6548</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>657.8663083905572</v>
+        <v>658.9680966894821</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>347</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>69.25148692129122</v>
+        <v>60.45098217602965</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.79091091413809</v>
+        <v>39.3282293003697</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.225488841196929</v>
+        <v>1.078183542491438</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.585940143775408</v>
+        <v>-1.605318531100165</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6573</v>
+        <v>6491</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>656.497966685445</v>
+        <v>657.8663083905572</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23.1</v>
+        <v>347</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.56048174675394</v>
+        <v>69.25148692129122</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.41370877123386</v>
+        <v>26.79091091413809</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.672231651085328</v>
+        <v>1.225488841196929</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.4893441192779733</v>
+        <v>1.585940143775408</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6658</v>
+        <v>6573</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>647.8517778191382</v>
+        <v>656.497966685445</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>231.5</v>
+        <v>23.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.77006771051652</v>
+        <v>72.56048174675394</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.26764272132431</v>
+        <v>27.41370877123386</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.273839377267725</v>
+        <v>1.672231651085328</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>4.657643782135629</v>
+        <v>0.4893441192779733</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6799</v>
+        <v>6658</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>640.5727710741755</v>
+        <v>647.8517778191382</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>102.5</v>
+        <v>231.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.08084339188484</v>
+        <v>62.77006771051652</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.55944091911315</v>
+        <v>31.26764272132431</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8684171017962092</v>
+        <v>2.273839377267725</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2140207603906812</v>
+        <v>4.657643782135629</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6525</v>
+        <v>6799</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>638.976764053683</v>
+        <v>640.5727710741755</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>166.5</v>
+        <v>102.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>67.96135436899482</v>
+        <v>56.08084339188484</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>35.23369374483058</v>
+        <v>23.55944091911315</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.930748519743361</v>
+        <v>0.8684171017962092</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.9918989212573665</v>
+        <v>0.2140207603906812</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6664</v>
+        <v>6525</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>637.998503693108</v>
+        <v>638.976764053683</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>408</v>
+        <v>166.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.33346188400159</v>
+        <v>67.96135436899482</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.41405948489945</v>
+        <v>35.23369374483058</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.248413721741592</v>
+        <v>0.930748519743361</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.925422763325424</v>
+        <v>0.9918989212573665</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6720</v>
+        <v>6664</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>637.7408800434973</v>
+        <v>637.998503693108</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>152</v>
+        <v>408</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.60661082277708</v>
+        <v>55.33346188400159</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.80436057365417</v>
+        <v>21.41405948489945</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.741123171897717</v>
+        <v>1.248413721741592</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.8113115008168652</v>
+        <v>3.925422763325424</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6831</v>
+        <v>6720</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>637.3142623178921</v>
+        <v>637.7408800434973</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>956</v>
+        <v>152</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>69.37216733834228</v>
+        <v>58.60661082277708</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>29.04175301682221</v>
+        <v>28.80436057365417</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.347546993846985</v>
+        <v>2.741123171897717</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>10.66899307223944</v>
+        <v>0.8113115008168652</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6757</v>
+        <v>6831</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>631.8230854876465</v>
+        <v>637.3142623178921</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>60.8</v>
+        <v>956</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.50968946030516</v>
+        <v>69.37216733834228</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>36.50041540735753</v>
+        <v>29.04175301682221</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3779877239474779</v>
+        <v>1.347546993846985</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.101537059350051</v>
+        <v>10.66899307223944</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6625</v>
+        <v>6757</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>629.1201862824601</v>
+        <v>631.8230854876465</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>79.2</v>
+        <v>60.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>62.07443807186985</v>
+        <v>56.50968946030516</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.59012452094372</v>
+        <v>36.50041540735753</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.446778076176744</v>
+        <v>0.3779877239474779</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0273672161148859</v>
+        <v>0.101537059350051</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6669</v>
+        <v>6625</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>618.5392255525509</v>
+        <v>629.1201862824601</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5200</v>
+        <v>79.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.27733826961894</v>
+        <v>62.07443807186985</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>16.59728441308083</v>
+        <v>29.59012452094372</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.487286226342269</v>
+        <v>0.446778076176744</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>9.140180831754876</v>
+        <v>0.0273672161148859</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6494</v>
+        <v>6669</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>615.9773138131966</v>
+        <v>618.5392255525509</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>67.7</v>
+        <v>5200</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.6051156413354</v>
+        <v>56.27733826961894</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>32.75375864245702</v>
+        <v>16.59728441308083</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6151723281600004</v>
+        <v>1.487286226342269</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.1085453834254521</v>
+        <v>9.140180831754876</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6716</v>
+        <v>6494</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>603.8233742727471</v>
+        <v>615.9773138131966</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>96.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>50.53996858604737</v>
+        <v>62.6051156413354</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.54648610264499</v>
+        <v>32.75375864245702</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5044773786704299</v>
+        <v>0.6151723281600004</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>1</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.7626818567370975</v>
+        <v>-0.1085453834254521</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6742</v>
+        <v>6716</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>595.5695063760779</v>
+        <v>603.8233742727471</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>66.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.27994255526022</v>
+        <v>50.53996858604737</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>33.37818925979427</v>
+        <v>20.54648610264499</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2378333377716121</v>
+        <v>0.5044773786704299</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.4708280321267351</v>
+        <v>-0.7626818567370975</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6585</v>
+        <v>6742</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>594.949629088351</v>
+        <v>595.5695063760779</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>128.5</v>
+        <v>66.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.84361505346816</v>
+        <v>57.27994255526022</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>49.59654201994663</v>
+        <v>33.37818925979427</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2123975838478481</v>
+        <v>0.2378333377716121</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-2.322895999487613</v>
+        <v>-0.4708280321267351</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6753</v>
+        <v>6585</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>592.8402008479877</v>
+        <v>594.949629088351</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>140</v>
+        <v>128.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.0760237665548</v>
+        <v>55.84361505346816</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.03068079320952</v>
+        <v>49.59654201994663</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.384020084798765</v>
+        <v>0.2123975838478481</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.474944977103058</v>
+        <v>-2.322895999487613</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6668</v>
+        <v>6753</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>591.193556765146</v>
+        <v>592.8402008479877</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>38.85</v>
+        <v>140</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46.15295402411331</v>
+        <v>66.0760237665548</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.91366517235675</v>
+        <v>20.03068079320952</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1834831157564411</v>
+        <v>3.384020084798765</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5747438875976916</v>
+        <v>2.474944977103058</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6654</v>
+        <v>6668</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>572.8149295096198</v>
+        <v>591.193556765146</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>186</v>
+        <v>38.85</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58.93598903202894</v>
+        <v>46.15295402411331</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>44.52388305047371</v>
+        <v>22.91366517235675</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3722303349068168</v>
+        <v>0.1834831157564411</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-4.672519686075152</v>
+        <v>-0.5747438875976916</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6732</v>
+        <v>6654</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>572.8058143957297</v>
+        <v>572.8149295096198</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.78697631652577</v>
+        <v>58.93598903202894</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>17.24493889678215</v>
+        <v>44.52388305047371</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.401769776504548</v>
+        <v>0.3722303349068168</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.003361076604251</v>
+        <v>-4.672519686075152</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6739</v>
+        <v>6732</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>571.3804637874833</v>
+        <v>572.8058143957297</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1200</v>
+        <v>173</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.68160705804532</v>
+        <v>58.78697631652577</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10.6764119610164</v>
+        <v>17.24493889678215</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.591849838495643</v>
+        <v>1.401769776504548</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>7.135787660337485</v>
+        <v>1.003361076604251</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6790</v>
+        <v>6739</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>570.1683858037004</v>
+        <v>571.3804637874833</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>40.6</v>
+        <v>1200</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.98378751586586</v>
+        <v>52.68160705804532</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.58012276767674</v>
+        <v>10.6764119610164</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.317344707172312</v>
+        <v>1.591849838495643</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0799887348327291</v>
+        <v>7.135787660337485</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6584</v>
+        <v>6790</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>566.9420743289701</v>
+        <v>570.1683858037004</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>743</v>
+        <v>40.6</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.34346681423442</v>
+        <v>58.98378751586586</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.1968470507443</v>
+        <v>24.58012276767674</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.347132029427237</v>
+        <v>1.317344707172312</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>11.59249798300368</v>
+        <v>0.0799887348327291</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6667</v>
+        <v>6584</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>561.4106036441484</v>
+        <v>566.9420743289701</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>268</v>
+        <v>743</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.07376371181419</v>
+        <v>59.34346681423442</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.0205557763113</v>
+        <v>16.1968470507443</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3520138235816272</v>
+        <v>1.347132029427237</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.479994286481098</v>
+        <v>11.59249798300368</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6684</v>
+        <v>6667</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>560.9004861180761</v>
+        <v>561.4106036441484</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>60.5</v>
+        <v>268</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.51531073636242</v>
+        <v>49.07376371181419</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>38.89283774875055</v>
+        <v>11.0205557763113</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.26924824768682</v>
+        <v>0.3520138235816272</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7061735383601602</v>
+        <v>-1.479994286481098</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6645</v>
+        <v>6684</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>554.6324929044647</v>
+        <v>560.9004861180761</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15.7</v>
+        <v>60.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>61.01896138261953</v>
+        <v>61.51531073636242</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>50.58205614417959</v>
+        <v>38.89283774875055</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.1416540681162255</v>
+        <v>1.26924824768682</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0284935571185565</v>
+        <v>0.7061735383601602</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6517</v>
+        <v>6645</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>551.2526438189875</v>
+        <v>554.6324929044647</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.5</v>
+        <v>15.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.44178415715422</v>
+        <v>61.01896138261953</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.12918619589966</v>
+        <v>50.58205614417959</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2354666811945221</v>
+        <v>0.1416540681162255</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,48 +2372,48 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.6985322320600877</v>
+        <v>0.0284935571185565</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6806</v>
+        <v>6517</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>548.7768356926886</v>
+        <v>551.2526438189875</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3.51</v>
+        <v>69.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>31.69502787830028</v>
+        <v>51.44178415715422</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.59319615579723</v>
+        <v>30.12918619589966</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.2354666811945221</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,48 +2425,48 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4112821530911623</v>
+        <v>-0.6985322320600877</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6538</v>
+        <v>6806</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>545.7356091877299</v>
+        <v>548.7768356926886</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>137</v>
+        <v>3.51</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>61.33414303514552</v>
+        <v>31.69502787830028</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>33.25460597258481</v>
+        <v>32.59319615579723</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.188655867526727</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.502677853977031</v>
+        <v>0.4112821530911623</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6670</v>
+        <v>6538</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>534.1093830856031</v>
+        <v>545.7356091877299</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>254.5</v>
+        <v>137</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.37087360780045</v>
+        <v>61.33414303514552</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>26.64176667873006</v>
+        <v>33.25460597258481</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4399905435367268</v>
+        <v>1.188655867526727</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-3.763573104874685</v>
+        <v>1.502677853977031</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6743</v>
+        <v>6670</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>530.8139803432763</v>
+        <v>534.1093830856031</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>31.5</v>
+        <v>254.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>62.33860457234822</v>
+        <v>42.37087360780045</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.08986861553993</v>
+        <v>26.64176667873006</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.958888427640822</v>
+        <v>0.4399905435367268</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1756889535830372</v>
+        <v>-3.763573104874685</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6666</v>
+        <v>6743</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>515.1113722463776</v>
+        <v>530.8139803432763</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>43.1</v>
+        <v>31.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.69563798380842</v>
+        <v>62.33860457234822</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>43.09398138301637</v>
+        <v>27.08986861553993</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7362600937484273</v>
+        <v>1.958888427640822</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0061078997778547</v>
+        <v>0.1756889535830372</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6698</v>
+        <v>6666</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>514.2559103166872</v>
+        <v>515.1113722463776</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>41.85</v>
+        <v>43.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.16396886183743</v>
+        <v>55.69563798380842</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>33.25779181589065</v>
+        <v>43.09398138301637</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3529712131228593</v>
+        <v>0.7362600937484273</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.303037750968711</v>
+        <v>0.0061078997778547</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6788</v>
+        <v>6698</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>511.8478047629927</v>
+        <v>514.2559103166872</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>440</v>
+        <v>41.85</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.35537598588169</v>
+        <v>53.16396886183743</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7.988935758622432</v>
+        <v>33.25779181589065</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7065794880673153</v>
+        <v>0.3529712131228593</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.09373495596124649</v>
+        <v>-0.303037750968711</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6568</v>
+        <v>6788</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>508.1188918334444</v>
+        <v>511.8478047629927</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>161</v>
+        <v>440</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>33.62497860384377</v>
+        <v>52.35537598588169</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>33.59834973501341</v>
+        <v>7.988935758622432</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3440061751598707</v>
+        <v>0.7065794880673153</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.3497950921741299</v>
+        <v>0.09373495596124649</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6725</v>
+        <v>6568</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>507.9333342568848</v>
+        <v>508.1188918334444</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>345</v>
+        <v>161</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.79995320988543</v>
+        <v>33.62497860384377</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.43434766149668</v>
+        <v>33.59834973501341</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3215471305615798</v>
+        <v>0.3440061751598707</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>2.671823819946738</v>
+        <v>-0.3497950921741299</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6531</v>
+        <v>6725</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>494.4845798312165</v>
+        <v>507.9333342568848</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>961</v>
+        <v>345</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.46227644890998</v>
+        <v>56.79995320988543</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.13763261552706</v>
+        <v>24.43434766149668</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5785465362473746</v>
+        <v>0.3215471305615798</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-9.350554589807205</v>
+        <v>2.671823819946738</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6782</v>
+        <v>6531</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>491.2306304213283</v>
+        <v>494.4845798312165</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>199.5</v>
+        <v>961</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.91360425790931</v>
+        <v>47.46227644890998</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>8.088047829462024</v>
+        <v>24.13763261552706</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.052978071111435</v>
+        <v>0.5785465362473746</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.7880057659813704</v>
+        <v>-9.350554589807205</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6579</v>
+        <v>6782</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>490.6315667985304</v>
+        <v>491.2306304213283</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>161.5</v>
+        <v>199.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.04536839934344</v>
+        <v>55.91360425790931</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.36980384067112</v>
+        <v>8.088047829462024</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7747859587556652</v>
+        <v>1.052978071111435</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.452811915009924</v>
+        <v>0.7880057659813704</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6582</v>
+        <v>6579</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>490.2030085190567</v>
+        <v>490.6315667985304</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>33</v>
+        <v>161.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>64.35914389272502</v>
+        <v>54.04536839934344</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>33.8471581205004</v>
+        <v>21.36980384067112</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4312640435701361</v>
+        <v>0.7747859587556652</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1196325635652444</v>
+        <v>-1.452811915009924</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6829</v>
+        <v>6582</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>489.8297399106085</v>
+        <v>490.2030085190567</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>220.5</v>
+        <v>33</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.27263954320628</v>
+        <v>64.35914389272502</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.32796192819997</v>
+        <v>33.8471581205004</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7600352985650458</v>
+        <v>0.4312640435701361</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.465650134820623</v>
+        <v>0.1196325635652444</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6770</v>
+        <v>6829</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>483.7579000767623</v>
+        <v>489.8297399106085</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>74.7</v>
+        <v>220.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.44839641367354</v>
+        <v>54.27263954320628</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.88304965078772</v>
+        <v>14.32796192819997</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7417766721247164</v>
+        <v>0.7600352985650458</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.5342510170494355</v>
+        <v>1.465650134820623</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6515</v>
+        <v>6770</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>482.9033611880789</v>
+        <v>483.7579000767623</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9310</v>
+        <v>74.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.40440285240897</v>
+        <v>50.44839641367354</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.62569562916472</v>
+        <v>22.88304965078772</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.574278280738472</v>
+        <v>0.7417766721247164</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-28.63150667621414</v>
+        <v>-0.5342510170494355</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6643</v>
+        <v>6515</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>480.5212648603168</v>
+        <v>482.9033611880789</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>498.5</v>
+        <v>9310</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.26228466656229</v>
+        <v>53.40440285240897</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.90418044157312</v>
+        <v>17.62569562916472</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6649106126965819</v>
+        <v>1.574278280738472</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.418720152000645</v>
+        <v>-28.63150667621414</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6679</v>
+        <v>6643</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>474.0741971005034</v>
+        <v>480.5212648603168</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>271.5</v>
+        <v>498.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.0634139794257</v>
+        <v>47.26228466656229</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.95835929854898</v>
+        <v>21.90418044157312</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.38759658847904</v>
+        <v>0.6649106126965819</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.5567605931938138</v>
+        <v>2.418720152000645</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6642</v>
+        <v>6679</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>457.1952703168857</v>
+        <v>474.0741971005034</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>271.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.14669978398936</v>
+        <v>45.0634139794257</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>34.6203086847321</v>
+        <v>17.95835929854898</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1487814629983865</v>
+        <v>0.38759658847904</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.259918633685526</v>
+        <v>-0.5567605931938138</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6640</v>
+        <v>6642</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>455.1876519552524</v>
+        <v>457.1952703168857</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1170</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.01626632628548</v>
+        <v>50.14669978398936</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.67414778531581</v>
+        <v>34.6203086847321</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.392379739476252</v>
+        <v>0.1487814629983865</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>16.65053013120223</v>
+        <v>-1.259918633685526</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6830</v>
+        <v>6640</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>447.8203323292512</v>
+        <v>455.1876519552524</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>448</v>
+        <v>1170</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>33.27712393714479</v>
+        <v>52.01626632628548</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.63372803193973</v>
+        <v>22.67414778531581</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9862797284675996</v>
+        <v>3.392379739476252</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-3.836726440217546</v>
+        <v>16.65053013120223</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6781</v>
+        <v>6830</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>437.3183916581081</v>
+        <v>447.8203323292512</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1205</v>
+        <v>448</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.68086700352517</v>
+        <v>33.27712393714479</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.19196096034464</v>
+        <v>22.63372803193973</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6884826467542839</v>
+        <v>0.9862797284675996</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.891691899387636</v>
+        <v>-3.836726440217546</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6792</v>
+        <v>6781</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>436.3855924148077</v>
+        <v>437.3183916581081</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>64.7</v>
+        <v>1205</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.26970707253389</v>
+        <v>54.68086700352517</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.15210812590854</v>
+        <v>11.19196096034464</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7725880314246435</v>
+        <v>0.6884826467542839</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.6568005261231995</v>
+        <v>2.891691899387636</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6695</v>
+        <v>6792</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>430.4982348304988</v>
+        <v>436.3855924148077</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>58.7</v>
+        <v>64.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.60814637264171</v>
+        <v>47.26970707253389</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.17439979474761</v>
+        <v>23.15210812590854</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8142155412216318</v>
+        <v>0.7725880314246435</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1995115367797577</v>
+        <v>-0.6568005261231995</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6597</v>
+        <v>6695</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>428.8625510265795</v>
+        <v>430.4982348304988</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>65</v>
+        <v>58.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.61875899235132</v>
+        <v>52.60814637264171</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11.69339865324672</v>
+        <v>26.17439979474761</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1857216946545773</v>
+        <v>0.8142155412216318</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.617515834121674</v>
+        <v>-0.1995115367797577</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6811</v>
+        <v>6597</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>428.4002352650373</v>
+        <v>428.8625510265795</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>219.5</v>
+        <v>65</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.47314680467571</v>
+        <v>42.61875899235132</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.00450953855042</v>
+        <v>11.69339865324672</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.098013698645183</v>
+        <v>0.1857216946545773</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.460261200337389</v>
+        <v>-0.617515834121674</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6556</v>
+        <v>6811</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>421.9752159908662</v>
+        <v>428.4002352650373</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>219.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.990699998942</v>
+        <v>50.47314680467571</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>30.53451851816559</v>
+        <v>20.00450953855042</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3733469352210099</v>
+        <v>1.098013698645183</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.225445585966371</v>
+        <v>-2.460261200337389</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6641</v>
+        <v>6556</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>409</v>
+        <v>421.9752159908662</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>18.15</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.49838931620789</v>
+        <v>47.990699998942</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.13150070854888</v>
+        <v>30.53451851816559</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.678206508116715</v>
+        <v>0.3733469352210099</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.019936985193468</v>
+        <v>-0.225445585966371</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6530</v>
+        <v>6641</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>408.7527981467733</v>
+        <v>409</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>84.5</v>
+        <v>18.15</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>35.15124855740217</v>
+        <v>46.49838931620789</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.3193582796863</v>
+        <v>15.13150070854888</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4073454416581599</v>
+        <v>7.678206508116715</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.055685949805934</v>
+        <v>-0.019936985193468</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6512</v>
+        <v>6530</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>398.8444397035099</v>
+        <v>408.7527981467733</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>27.9504893677836</v>
+        <v>35.15124855740217</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9.943023644942784</v>
+        <v>24.3193582796863</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.0453455346107568</v>
+        <v>0.4073454416581599</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.043111085971275</v>
+        <v>-1.055685949805934</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6821</v>
+        <v>6512</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>398.8342679349746</v>
+        <v>398.8444397035099</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>60.5</v>
+        <v>0</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.51815628418582</v>
+        <v>27.9504893677836</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.86024990957302</v>
+        <v>9.943023644942784</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7230830953685947</v>
+        <v>0.0453455346107568</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.7301432478812837</v>
+        <v>-1.043111085971275</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6510</v>
+        <v>6821</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>393.5123364349108</v>
+        <v>398.8342679349746</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>3240</v>
+        <v>60.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.54327126075185</v>
+        <v>45.51815628418582</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.31473834126664</v>
+        <v>16.86024990957302</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8250582892281815</v>
+        <v>0.7230830953685947</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-29.49338152221121</v>
+        <v>-0.7301432478812837</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6589</v>
+        <v>6510</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>390.7779499376076</v>
+        <v>393.5123364349108</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46.9</v>
+        <v>3240</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.02754718138739</v>
+        <v>45.54327126075185</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.42628036384899</v>
+        <v>17.31473834126664</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.113856427855566</v>
+        <v>0.8250582892281815</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3199855319497522</v>
+        <v>-29.49338152221121</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6533</v>
+        <v>6589</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>386.166053769747</v>
+        <v>390.7779499376076</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>202</v>
+        <v>46.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.04094149111404</v>
+        <v>53.02754718138739</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.42177296189289</v>
+        <v>20.42628036384899</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6722345913317489</v>
+        <v>1.113856427855566</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0741733767691998</v>
+        <v>0.3199855319497522</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6741</v>
+        <v>6533</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>379.7650285258893</v>
+        <v>386.166053769747</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>60.9</v>
+        <v>202</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.50447718447803</v>
+        <v>46.04094149111404</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.98847141808981</v>
+        <v>11.42177296189289</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3980596511830202</v>
+        <v>0.6722345913317489</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1357411594333769</v>
+        <v>0.0741733767691998</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6823</v>
+        <v>6715</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>376.6971996285649</v>
+        <v>382.0925100783574</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>71.2</v>
+        <v>445</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.29325053683674</v>
+        <v>48.95819245949966</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.85858791137275</v>
+        <v>18.63887205032377</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.300234199449315</v>
+        <v>0.1671988667187419</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.5612111459546401</v>
+        <v>-3.467724124226639</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6598</v>
+        <v>6741</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>374.6509824968695</v>
+        <v>379.7650285258893</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>22.75</v>
+        <v>60.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>35.82822625552879</v>
+        <v>44.50447718447803</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.05075770729002</v>
+        <v>8.98847141808981</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4747780210020249</v>
+        <v>0.3980596511830202</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1981573728075635</v>
+        <v>-0.1357411594333769</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6592</v>
+        <v>6823</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>366.2465878736859</v>
+        <v>376.6971996285649</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>59</v>
+        <v>71.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>30.96062773265414</v>
+        <v>50.29325053683674</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.68733788134192</v>
+        <v>18.85858791137275</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6314132876470404</v>
+        <v>2.300234199449315</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.8929143817993486</v>
+        <v>0.5612111459546401</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6588</v>
+        <v>6598</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>357.7180296528136</v>
+        <v>374.6509824968695</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>85.2</v>
+        <v>22.75</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>28.47759435563208</v>
+        <v>35.82822625552879</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.01942135522389</v>
+        <v>21.05075770729002</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4761212997185052</v>
+        <v>0.4747780210020249</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.205450867760053</v>
+        <v>-0.1981573728075635</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6768</v>
+        <v>6592</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>348.7431870798413</v>
+        <v>366.2465878736859</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>72.5</v>
+        <v>59</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>25.81653850182218</v>
+        <v>30.96062773265414</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.61636915367345</v>
+        <v>30.68733788134192</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7759205938788347</v>
+        <v>0.6314132876470404</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.035140552729368</v>
+        <v>-0.8929143817993486</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6504</v>
+        <v>6588</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>345.5440321336513</v>
+        <v>357.7180296528136</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>35.8</v>
+        <v>85.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.70826423181557</v>
+        <v>28.47759435563208</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.19270447029063</v>
+        <v>20.01942135522389</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8710451974315221</v>
+        <v>0.4761212997185052</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.08352962156749009</v>
+        <v>-1.205450867760053</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6655</v>
+        <v>6768</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>341.6868009440784</v>
+        <v>348.7431870798413</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>120</v>
+        <v>72.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.09511581601376</v>
+        <v>25.81653850182218</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.49694168535403</v>
+        <v>22.61636915367345</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8593393477726682</v>
+        <v>0.7759205938788347</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1.847086297517387</v>
+        <v>-2.035140552729368</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6605</v>
+        <v>6504</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>336.3794228245974</v>
+        <v>345.5440321336513</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>133</v>
+        <v>35.8</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.82132576552848</v>
+        <v>38.70826423181557</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.36814523785074</v>
+        <v>17.19270447029063</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8441780972616443</v>
+        <v>0.8710451974315221</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.351850947934233</v>
+        <v>0.08352962156749009</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6570</v>
+        <v>6655</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>334.0364080828401</v>
+        <v>341.6868009440784</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.8006967250967</v>
+        <v>50.09511581601376</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>24.26654108921397</v>
+        <v>10.49694168535403</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.146831456438137</v>
+        <v>0.8593393477726682</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.7224495453370564</v>
+        <v>1.847086297517387</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6690</v>
+        <v>6605</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>330.5112036378154</v>
+        <v>336.3794228245974</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.65420884863382</v>
+        <v>40.82132576552848</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.74922567534837</v>
+        <v>14.36814523785074</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4391179305822773</v>
+        <v>0.8441780972616443</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.91388206243487</v>
+        <v>-1.351850947934233</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6789</v>
+        <v>6570</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>324.9797476921088</v>
+        <v>334.0364080828401</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>530</v>
+        <v>54</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>52.83738429151181</v>
+        <v>53.8006967250967</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.0688920372182</v>
+        <v>24.26654108921397</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5268422488429859</v>
+        <v>1.146831456438137</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.71279382049703</v>
+        <v>-0.7224495453370564</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6498</v>
+        <v>6690</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>309.8590643846239</v>
+        <v>330.5112036378154</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>94.8</v>
+        <v>164</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.10053790110426</v>
+        <v>39.65420884863382</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.87208859336247</v>
+        <v>18.74922567534837</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3012178780517345</v>
+        <v>0.4391179305822773</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.244669399492465</v>
+        <v>-1.91388206243487</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6624</v>
+        <v>6789</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>305.4043825646938</v>
+        <v>324.9797476921088</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>44.85</v>
+        <v>530</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.44640847130836</v>
+        <v>52.83738429151181</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.676841010839436</v>
+        <v>14.0688920372182</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>3.327211927346029</v>
+        <v>0.5268422488429859</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.339118242984265</v>
+        <v>1.71279382049703</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6532</v>
+        <v>6498</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>303.2469961134014</v>
+        <v>309.8590643846239</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>91.8</v>
+        <v>94.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.2864490389058</v>
+        <v>43.10053790110426</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.18180731862965</v>
+        <v>21.87208859336247</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4464196540309972</v>
+        <v>0.3012178780517345</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.2972401306886145</v>
+        <v>-1.244669399492465</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6754</v>
+        <v>6624</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>297.9822714339788</v>
+        <v>305.4043825646938</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>45.4</v>
+        <v>44.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.19935418591347</v>
+        <v>52.44640847130836</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.86506214553845</v>
+        <v>9.676841010839436</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7926737727068008</v>
+        <v>3.327211927346029</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0220492089798344</v>
+        <v>1.339118242984265</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6727</v>
+        <v>6532</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>289.8890971674577</v>
+        <v>303.2469961134014</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>412.5</v>
+        <v>91.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.14193091807392</v>
+        <v>49.2864490389058</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.17288125302214</v>
+        <v>16.18180731862965</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2637909237462018</v>
+        <v>0.4464196540309972</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.438525691362887</v>
+        <v>0.2972401306886145</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6776</v>
+        <v>6754</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>288.8755531123426</v>
+        <v>297.9822714339788</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>53.8</v>
+        <v>45.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>30.43758774151202</v>
+        <v>54.19935418591347</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.63931538958428</v>
+        <v>17.86506214553845</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3136820301364355</v>
+        <v>0.7926737727068008</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.6353902565800732</v>
+        <v>-0.0220492089798344</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6541</v>
+        <v>6727</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>284.2155202145318</v>
+        <v>289.8890971674577</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.55</v>
+        <v>412.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>50.00708316833753</v>
+        <v>44.14193091807392</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.85605335820415</v>
+        <v>13.17288125302214</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.566777106399867</v>
+        <v>0.2637909237462018</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1428526338661084</v>
+        <v>-1.438525691362887</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6761</v>
+        <v>6776</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>281.0319642853985</v>
+        <v>288.8755531123426</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>194.5</v>
+        <v>53.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.31276911322875</v>
+        <v>30.43758774151202</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.62350831462696</v>
+        <v>18.63931538958428</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5724059452686205</v>
+        <v>0.3136820301364355</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.835067903022185</v>
+        <v>-0.6353902565800732</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6486</v>
+        <v>6541</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>278.838663772432</v>
+        <v>284.2155202145318</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>81.8</v>
+        <v>40.55</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.5948932118174</v>
+        <v>50.00708316833753</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.44291061903159</v>
+        <v>15.85605335820415</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5259167470259178</v>
+        <v>0.566777106399867</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1001958122969424</v>
+        <v>-0.1428526338661084</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6606</v>
+        <v>6761</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>274.7940876727803</v>
+        <v>281.0319642853985</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>24.9</v>
+        <v>194.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.36566502814852</v>
+        <v>48.31276911322875</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.63471746941254</v>
+        <v>15.62350831462696</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.8945075104977372</v>
+        <v>0.5724059452686205</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.09316529085564849</v>
+        <v>-1.835067903022185</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6756</v>
+        <v>6486</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>269.8414475790453</v>
+        <v>278.838663772432</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>98.5</v>
+        <v>81.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>50.55861074853773</v>
+        <v>48.5948932118174</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.97122749304255</v>
+        <v>13.44291061903159</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3226089849433703</v>
+        <v>0.5259167470259178</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.6554842668755765</v>
+        <v>0.1001958122969424</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6550</v>
+        <v>6606</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>265.9765455418318</v>
+        <v>274.7940876727803</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>13.15</v>
+        <v>24.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.88794888237413</v>
+        <v>42.36566502814852</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.41044820033472</v>
+        <v>16.63471746941254</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.820173869066421</v>
+        <v>0.8945075104977372</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1791919759151613</v>
+        <v>-0.09316529085564849</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6706</v>
+        <v>6756</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>260.3026661485801</v>
+        <v>269.8414475790453</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>149.5</v>
+        <v>98.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.82728850665878</v>
+        <v>50.55861074853773</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.31441975869014</v>
+        <v>19.97122749304255</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3343073963620409</v>
+        <v>0.3226089849433703</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-2.636225625415684</v>
+        <v>-0.6554842668755765</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6692</v>
+        <v>6550</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>260.153455999975</v>
+        <v>265.9765455418318</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>25.7</v>
+        <v>13.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.05334257694972</v>
+        <v>41.88794888237413</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15.17548720329403</v>
+        <v>25.41044820033472</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3052848716653953</v>
+        <v>0.820173869066421</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1267767441184009</v>
+        <v>0.1791919759151613</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6805</v>
+        <v>6706</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>254.5070966867004</v>
+        <v>260.3026661485801</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1670</v>
+        <v>149.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>42.51308522889925</v>
+        <v>40.82728850665878</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.28397155924686</v>
+        <v>17.31441975869014</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.127331400285058</v>
+        <v>0.3343073963620409</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-10.41900502821714</v>
+        <v>-2.636225625415684</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6835</v>
+        <v>6692</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>248.547673000955</v>
+        <v>260.153455999975</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>34.8</v>
+        <v>25.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.94278637867784</v>
+        <v>42.05334257694972</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.40286387063915</v>
+        <v>15.17548720329403</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4405114222469763</v>
+        <v>0.3052848716653953</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1747485551413221</v>
+        <v>0.1267767441184009</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6708</v>
+        <v>6805</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>246.760457377148</v>
+        <v>254.5070966867004</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>39.8</v>
+        <v>1670</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.81948459315269</v>
+        <v>42.51308522889925</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.03546767504414</v>
+        <v>15.28397155924686</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1978655800802524</v>
+        <v>1.127331400285058</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.08591797289215369</v>
+        <v>-10.41900502821714</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6735</v>
+        <v>6835</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>242.4555201224938</v>
+        <v>248.547673000955</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>88.2</v>
+        <v>34.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.2178567929214</v>
+        <v>34.94278637867784</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.07746870218834</v>
+        <v>24.40286387063915</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.362940475701006</v>
+        <v>0.4405114222469763</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1479344861631597</v>
+        <v>-0.1747485551413221</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6657</v>
+        <v>6708</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>226.8602803293095</v>
+        <v>246.760457377148</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>35.4</v>
+        <v>39.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>42.48837313015695</v>
+        <v>46.81948459315269</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.04970326901995</v>
+        <v>15.03546767504414</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3148031703819627</v>
+        <v>0.1978655800802524</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1820961620703807</v>
+        <v>0.08591797289215369</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6577</v>
+        <v>6735</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>220.4380123100279</v>
+        <v>242.4555201224938</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.30374301752061</v>
+        <v>40.2178567929214</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.13219724771228</v>
+        <v>11.07746870218834</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1631047617933465</v>
+        <v>0.362940475701006</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2931924000000825</v>
+        <v>-0.1479344861631597</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6614</v>
+        <v>6657</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>217.0964818716249</v>
+        <v>226.8602803293095</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>39.95</v>
+        <v>35.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.98863227236658</v>
+        <v>42.48837313015695</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.20830189134099</v>
+        <v>22.04970326901995</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.8873950926486852</v>
+        <v>0.3148031703819627</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0236611327339921</v>
+        <v>0.1820961620703807</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6722</v>
+        <v>6577</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>212.6374162887288</v>
+        <v>220.4380123100279</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>34.25</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>30.94064155029312</v>
+        <v>39.30374301752061</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>31.21675445731109</v>
+        <v>23.13219724771228</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5199193273789255</v>
+        <v>0.1631047617933465</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.3181370152412455</v>
+        <v>-0.2931924000000825</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6771</v>
+        <v>6614</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>212.1525702317069</v>
+        <v>217.0964818716249</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>38.75</v>
+        <v>39.95</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>32.40646699370473</v>
+        <v>48.98863227236658</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.42809959482959</v>
+        <v>17.20830189134099</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.065206870121179</v>
+        <v>0.8873950926486852</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2613890240368579</v>
+        <v>-0.0236611327339921</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6581</v>
+        <v>6722</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>196.7633519119888</v>
+        <v>212.6374162887288</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>106.5</v>
+        <v>34.25</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.3189262964496</v>
+        <v>30.94064155029312</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11.90158741657898</v>
+        <v>31.21675445731109</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8237294007226614</v>
+        <v>0.5199193273789255</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2288932207787248</v>
+        <v>-0.3181370152412455</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6552</v>
+        <v>6771</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>194.743107889435</v>
+        <v>212.1525702317069</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>30.8</v>
+        <v>38.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>50.27934375724336</v>
+        <v>32.40646699370473</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.68257093543568</v>
+        <v>22.42809959482959</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6762680437599415</v>
+        <v>1.065206870121179</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0979846265706423</v>
+        <v>-0.2613890240368579</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6534</v>
+        <v>6581</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>192.0472892407923</v>
+        <v>196.7633519119888</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>89.8</v>
+        <v>106.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.90331156828036</v>
+        <v>43.3189262964496</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.4547868705333</v>
+        <v>11.90158741657898</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6261283788402658</v>
+        <v>0.8237294007226614</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0127511022999701</v>
+        <v>-0.2288932207787248</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6796</v>
+        <v>6552</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>189.525222990329</v>
+        <v>194.743107889435</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>58.1</v>
+        <v>30.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.8471952917473</v>
+        <v>50.27934375724336</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>27.23039746727326</v>
+        <v>12.68257093543568</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3152761181963404</v>
+        <v>0.6762680437599415</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1406174912586228</v>
+        <v>-0.0979846265706423</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6561</v>
+        <v>6534</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>185.2297568956217</v>
+        <v>192.0472892407923</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>336.5</v>
+        <v>89.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.67103521902839</v>
+        <v>41.90331156828036</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.89043722163076</v>
+        <v>12.4547868705333</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5951019970327676</v>
+        <v>0.6261283788402658</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.3604029262904529</v>
+        <v>-0.0127511022999701</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6763</v>
+        <v>6796</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>165.3975827496865</v>
+        <v>189.525222990329</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>46.35</v>
+        <v>58.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.87945914035713</v>
+        <v>42.8471952917473</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.85574672244853</v>
+        <v>27.23039746727326</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3071704646501922</v>
+        <v>0.3152761181963404</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.109683966592034</v>
+        <v>0.1406174912586228</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6546</v>
+        <v>6561</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>160.4484605502173</v>
+        <v>185.2297568956217</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.8</v>
+        <v>336.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,49 +6382,49 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.92415172952993</v>
+        <v>43.67103521902839</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.11350960215466</v>
+        <v>18.89043722163076</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2464505593285634</v>
+        <v>0.5951019970327676</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M112" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.7281026872431113</v>
+        <v>-0.3604029262904529</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6680</v>
+        <v>6763</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>159.1124798252273</v>
+        <v>165.3975827496865</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>50.8</v>
+        <v>46.35</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.90936339670501</v>
+        <v>46.87945914035713</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>4.392691790575532</v>
+        <v>16.85574672244853</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5980283165351292</v>
+        <v>0.3071704646501922</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2667386097016991</v>
+        <v>-0.109683966592034</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6671</v>
+        <v>6546</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>150.8880875119939</v>
+        <v>160.4484605502173</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>24.8</v>
+        <v>69.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>32.49884200720614</v>
+        <v>42.92415172952993</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>29.36622373628132</v>
+        <v>15.11350960215466</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.0562331651961694</v>
+        <v>0.2464505593285634</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.036121216343654</v>
+        <v>-0.7281026872431113</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6840</v>
+        <v>6680</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>150.263711721133</v>
+        <v>159.1124798252273</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>63.1</v>
+        <v>50.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.32099809833228</v>
+        <v>50.90936339670501</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.97823147735909</v>
+        <v>4.392691790575532</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.1936070959893483</v>
+        <v>0.5980283165351292</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.3926569494567713</v>
+        <v>0.2667386097016991</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6558</v>
+        <v>6671</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>149.630727968868</v>
+        <v>150.8880875119939</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>29.45</v>
+        <v>24.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.7135367899989</v>
+        <v>32.49884200720614</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.90160540697021</v>
+        <v>29.36622373628132</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5403376992414491</v>
+        <v>0.0562331651961694</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2072680025036761</v>
+        <v>0.036121216343654</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6794</v>
+        <v>6840</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>144.1808392599329</v>
+        <v>150.263711721133</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>77.5</v>
+        <v>63.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.4508135458016</v>
+        <v>44.32099809833228</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.45347153838974</v>
+        <v>13.97823147735909</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.056923959271446</v>
+        <v>0.1936070959893483</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1203823284792385</v>
+        <v>-0.3926569494567713</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6838</v>
+        <v>6558</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>142.1929057259543</v>
+        <v>149.630727968868</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>23.9</v>
+        <v>29.45</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>37.97505308678637</v>
+        <v>44.7135367899989</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.0481020526151</v>
+        <v>20.90160540697021</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4196167775570443</v>
+        <v>0.5403376992414491</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0203692548449446</v>
+        <v>-0.2072680025036761</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6591</v>
+        <v>6794</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>132.0817857477006</v>
+        <v>144.1808392599329</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>54.9</v>
+        <v>77.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.18071248269585</v>
+        <v>37.4508135458016</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20.87770747074327</v>
+        <v>15.45347153838974</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5448967015979574</v>
+        <v>1.056923959271446</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0353398251864287</v>
+        <v>-0.1203823284792385</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6689</v>
+        <v>6838</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>121.8929696140109</v>
+        <v>142.1929057259543</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>62.6</v>
+        <v>23.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>33.42073310715094</v>
+        <v>37.97505308678637</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.25232454374652</v>
+        <v>13.0481020526151</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7306975589310563</v>
+        <v>0.4196167775570443</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.5348928980246974</v>
+        <v>0.0203692548449446</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6674</v>
+        <v>6591</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>96.00898867631244</v>
+        <v>132.0817857477006</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>16.85</v>
+        <v>54.9</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>40.14832008584604</v>
+        <v>49.18071248269585</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.65850785099871</v>
+        <v>20.87770747074327</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.285736291092198</v>
+        <v>0.5448967015979574</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,62 +6877,168 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0301627611338933</v>
+        <v>-0.0353398251864287</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>伊雲谷</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>121.8929696140109</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>33.42073310715094</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>16.25232454374652</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.7306975589310563</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.5348928980246974</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>6674</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>鋐寶科技</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>96.00898867631244</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>40.14832008584604</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>19.65850785099871</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.285736291092198</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.0301627611338933</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
         <v>6807</v>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>峰源-KY</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="n">
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
         <v>69.92640119454271</v>
       </c>
-      <c r="E122" s="2" t="n">
+      <c r="E124" s="2" t="n">
         <v>33.2</v>
       </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="n">
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
         <v>44.49907466942201</v>
       </c>
-      <c r="I122" s="2" t="n">
+      <c r="I124" s="2" t="n">
         <v>17.3680284342128</v>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J124" s="2" t="n">
         <v>0.3612124487681845</v>
       </c>
-      <c r="K122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" s="2" t="n">
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
         <v>0.1160465418988415</v>
       </c>
-      <c r="O122" s="2" t="inlineStr">
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
